--- a/static/excel/SNAP_model.xlsx
+++ b/static/excel/SNAP_model.xlsx
@@ -7766,16 +7766,16 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B45" s="55">
-        <f>B8*B28+B9*B38*(1-B42)</f>
+        <f>MAX(0.085, B8*B28+B9*B38*(1-B42))</f>
         <v/>
       </c>
       <c r="C45" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — SNAP  |  Master Prompt v2  |  23 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — SNAP  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>

--- a/static/excel/SNAP_model.xlsx
+++ b/static/excel/SNAP_model.xlsx
@@ -7383,11 +7383,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7597,25 +7597,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0698</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLH0A0HYM2EY — High Yield</t>
         </is>
       </c>
     </row>
@@ -7658,11 +7660,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.05890000000000001</v>
+        <v>0.05879999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 1.32%</t>
+          <t>Rf 4.56% + spread 1.32%</t>
         </is>
       </c>
     </row>
@@ -7701,11 +7703,11 @@
         </is>
       </c>
       <c r="B38" s="48" t="n">
-        <v>0.041</v>
+        <v>0.0505</v>
       </c>
       <c r="C38" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10022,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="113" t="inlineStr">
         <is>
-          <t>JS SCORECARD — SNAP  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — SNAP  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
